--- a/assets/data/imf/excel/ove_pib_fmi_ngdpd_precios_corrientes_dolares_estadounidenses.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdpd_precios_corrientes_dolares_estadounidenses.xlsx
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_ngdpd_precios_corrientes_dolares_estadounidenses.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdpd_precios_corrientes_dolares_estadounidenses.xlsx
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_ngdpd_precios_corrientes_dolares_estadounidenses.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdpd_precios_corrientes_dolares_estadounidenses.xlsx
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_ngdpd_precios_corrientes_dolares_estadounidenses.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdpd_precios_corrientes_dolares_estadounidenses.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -2492,7 +2492,7 @@
         <v>2007</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>232857191000</v>
+        <v>234942819000</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -2560,7 +2560,7 @@
         <v>2008</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>306764322000</v>
+        <v>303292888000</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -2628,7 +2628,7 @@
         <v>2009</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>268623668000</v>
+        <v>262260365000</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -2696,7 +2696,7 @@
         <v>2010</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>318280503000</v>
+        <v>303863387000</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -2764,7 +2764,7 @@
         <v>2011</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>316482410000</v>
+        <v>304551181000</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -2832,7 +2832,7 @@
         <v>2012</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>372591992000</v>
+        <v>338732097000</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -2900,7 +2900,7 @@
         <v>2013</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>258931842000</v>
+        <v>225506101000</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -2968,7 +2968,7 @@
         <v>2014</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>214689576000</v>
+        <v>128764356000</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -3036,7 +3036,7 @@
         <v>2015</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>125449472000</v>
+        <v>84286749000</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
@@ -3104,7 +3104,7 @@
         <v>2016</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>112914909000</v>
+        <v>78520608000</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
@@ -3172,7 +3172,7 @@
         <v>2017</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>115882145000</v>
+        <v>59976326000</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
@@ -3240,7 +3240,7 @@
         <v>2018</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>102020739000</v>
+        <v>47614201000</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>2019</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>73013796000</v>
+        <v>22370756000</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
@@ -3376,7 +3376,7 @@
         <v>2020</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>42837989000</v>
+        <v>20011656000</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -3444,7 +3444,7 @@
         <v>2021</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>56615017000</v>
+        <v>39136330000</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
@@ -3512,7 +3512,7 @@
         <v>2022</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>89013259000</v>
+        <v>79518928000</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -3580,7 +3580,7 @@
         <v>2023</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>102377526000</v>
+        <v>76762468000</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
@@ -3648,7 +3648,7 @@
         <v>2024</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>120566093000</v>
+        <v>103713018000</v>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
@@ -3716,7 +3716,7 @@
         <v>2025</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>99661235000</v>
+        <v>101491612000</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
@@ -3784,7 +3784,7 @@
         <v>2026</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>111303343000</v>
+        <v>124183629000</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -3852,7 +3852,7 @@
         <v>2027</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>117908128000</v>
+        <v>130649428000</v>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>117908128000</v>
+        <v>130649428000</v>
       </c>
     </row>
     <row r="18">

--- a/assets/data/imf/excel/ove_pib_fmi_ngdpd_precios_corrientes_dolares_estadounidenses.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdpd_precios_corrientes_dolares_estadounidenses.xlsx
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
